--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484847_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484847_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6785</v>
+        <v>2.0136</v>
       </c>
       <c r="E2" t="n">
-        <v>0.571</v>
+        <v>0.7473</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1075</v>
+        <v>1.2662</v>
       </c>
       <c r="G2" t="n">
         <v>-0.0051</v>
@@ -610,13 +610,13 @@
         <v>1.5096</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1552</v>
+        <v>0.4903</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3509</v>
       </c>
       <c r="V2" t="n">
         <v>0.9624</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CARR</t>
+          <t>D. KEITA DIALLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3732</v>
+        <v>1.2447</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1221</v>
+        <v>1.4709</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2511</v>
+        <v>-0.2263</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.2882</v>
+        <v>0.4749</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.8751</v>
+        <v>-1.1121</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5869</v>
+        <v>1.587</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.06850000000000001</v>
+        <v>1.7805</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8499</v>
+        <v>-0.1526</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7815</v>
+        <v>1.9331</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2198</v>
+        <v>-1.3055</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0252</v>
+        <v>-0.9595</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1946</v>
+        <v>-0.3461</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3774</v>
+        <v>0.5661</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S3" t="n">
-        <v>0.756</v>
+        <v>0.4864</v>
       </c>
       <c r="T3" t="n">
-        <v>0.606</v>
+        <v>0.634</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1499</v>
+        <v>-0.1475</v>
       </c>
       <c r="V3" t="n">
-        <v>1.528</v>
+        <v>-0.2828</v>
       </c>
       <c r="W3" t="n">
-        <v>1.528</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2828</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. KEITA DIALLO</t>
+          <t>J. CARR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2955</v>
+        <v>0.9977</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5482</v>
+        <v>0.6937</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2527</v>
+        <v>0.304</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4749</v>
+        <v>-1.2882</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1121</v>
+        <v>-1.8751</v>
       </c>
       <c r="I4" t="n">
-        <v>1.587</v>
+        <v>0.5869</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7805</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1526</v>
+        <v>-0.8499</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9331</v>
+        <v>0.7815</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3055</v>
+        <v>-1.2198</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9595</v>
+        <v>-1.0252</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3461</v>
+        <v>-0.1946</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5661</v>
+        <v>0.3774</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5373</v>
+        <v>0.3805</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.1776</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.174</v>
+        <v>0.2029</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2828</v>
+        <v>1.528</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.528</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0471</v>
+        <v>0.8665</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6085</v>
+        <v>1.375</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5614</v>
+        <v>-0.5085</v>
       </c>
       <c r="G5" t="n">
         <v>0.8108</v>
@@ -844,13 +844,13 @@
         <v>0.1887</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0476</v>
+        <v>-0.133</v>
       </c>
       <c r="T5" t="n">
-        <v>0.532</v>
+        <v>0.2985</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4844</v>
+        <v>-0.4315</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9127</v>
+        <v>-1.1341</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2789</v>
+        <v>1.084</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1916</v>
+        <v>-2.218</v>
       </c>
       <c r="G7" t="n">
         <v>-2.1231</v>
@@ -1000,13 +1000,13 @@
         <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>0.833</v>
+        <v>0.6116</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7824</v>
+        <v>0.5875</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0506</v>
+        <v>0.0241</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.948</v>
+        <v>-1.1731</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1998</v>
+        <v>-0.1312</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1478</v>
+        <v>-1.042</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5209</v>
@@ -1078,13 +1078,13 @@
         <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.4609</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6525</v>
+        <v>0.3215</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0335</v>
+        <v>0.1394</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9244</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FERRAGUT SEBASTIA</t>
+          <t>P. TORRES TOVAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1653</v>
+        <v>-2.8179</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3436</v>
+        <v>-4.4583</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8217</v>
+        <v>1.6405</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5684</v>
+        <v>-3.9018</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.391</v>
+        <v>0.1902</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8226</v>
+        <v>-4.092</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8933</v>
+        <v>-3.5116</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.098</v>
+        <v>0.3858</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9913</v>
+        <v>-3.8974</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4617</v>
+        <v>-0.3902</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.293</v>
+        <v>-0.1956</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1687</v>
+        <v>-0.1946</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1887</v>
+        <v>0.1887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6983</v>
+        <v>1.1322</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1064</v>
+        <v>0.2537</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3498</v>
+        <v>-0.0033</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2434</v>
+        <v>0.2569</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3018</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3018</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. SARRIAS SANCHEZ</t>
+          <t>A. FERRAGUT SEBASTIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4468</v>
+        <v>-2.8671</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7041</v>
+        <v>-0.9925</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7426</v>
+        <v>-1.8747</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.5706</v>
+        <v>-2.5684</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.4968</v>
+        <v>-3.391</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0737</v>
+        <v>0.8226</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0727</v>
+        <v>0.8933</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.7563</v>
+        <v>-1.098</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6836</v>
+        <v>1.9913</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4978</v>
+        <v>-3.4617</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7405</v>
+        <v>-2.293</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7574</v>
+        <v>-1.1687</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3774</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3209</v>
+        <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4256</v>
+        <v>0.1918</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3121</v>
+        <v>0.0013</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1135</v>
+        <v>0.1905</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3208</v>
+        <v>-0.3018</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3208</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. TORRES TOVAR</t>
+          <t>D. SARRIAS SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4613</v>
+        <v>-3.6358</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1017</v>
+        <v>-2.8402</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6405</v>
+        <v>-0.7956</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.9018</v>
+        <v>-4.5706</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1902</v>
+        <v>-4.4968</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.092</v>
+        <v>-0.0737</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.5116</v>
+        <v>-2.0727</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3858</v>
+        <v>-2.7563</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.8974</v>
+        <v>0.6836</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3902</v>
+        <v>-2.4978</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1956</v>
+        <v>-1.7405</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1946</v>
+        <v>-0.7574</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1322</v>
+        <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3897</v>
+        <v>0.2366</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.176</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2569</v>
+        <v>0.0606</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.3208</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7491</v>
+        <v>-3.991</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2448</v>
+        <v>-0.3809</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5043</v>
+        <v>-3.6101</v>
       </c>
       <c r="G12" t="n">
         <v>0.5369</v>
@@ -1390,13 +1390,13 @@
         <v>0.5661</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.154</v>
+        <v>-0.3959</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1793</v>
+        <v>0.0432</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3333</v>
+        <v>-0.4391</v>
       </c>
       <c r="V12" t="n">
         <v>-3.7546</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7207</v>
+        <v>-4.1953</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.4928</v>
+        <v>-4.8881</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7721</v>
+        <v>0.6927</v>
       </c>
       <c r="G13" t="n">
         <v>-3.4678</v>
@@ -1468,13 +1468,13 @@
         <v>1.6983</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2193</v>
+        <v>0.7446</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2199</v>
+        <v>0.3848</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4392</v>
+        <v>0.3598</v>
       </c>
       <c r="V13" t="n">
         <v>1.547</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.6662</v>
+        <v>-5.1021</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.4063</v>
+        <v>-3.7629</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2599</v>
+        <v>-1.3393</v>
       </c>
       <c r="G14" t="n">
         <v>-0.4778</v>
@@ -1546,13 +1546,13 @@
         <v>1.1322</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9993</v>
+        <v>-0.4353</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7055</v>
+        <v>-0.0621</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2939</v>
+        <v>-0.3732</v>
       </c>
       <c r="V14" t="n">
         <v>0.3398</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-20.0588</v>
+        <v>-19.1769</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.3478</v>
+        <v>-11.4662</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.710800000000001</v>
+        <v>-7.711099999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-16.4841</v>
@@ -1600,7 +1600,7 @@
         <v>2.5328</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5868000000000002</v>
+        <v>0.5867999999999998</v>
       </c>
       <c r="L15" t="n">
         <v>1.946</v>
@@ -1624,13 +1624,13 @@
         <v>14.1525</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0106</v>
+        <v>2.8922</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5184</v>
+        <v>3.4002</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5082</v>
+        <v>-0.508</v>
       </c>
       <c r="V15" t="n">
         <v>0.07600000000000018</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.4703</v>
+        <v>6.7089</v>
       </c>
       <c r="E16" t="n">
-        <v>6.7971</v>
+        <v>6.1151</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6732</v>
+        <v>0.5938</v>
       </c>
       <c r="G16" t="n">
         <v>7.4963</v>
@@ -1702,13 +1702,13 @@
         <v>2.0757</v>
       </c>
       <c r="S16" t="n">
-        <v>0.408</v>
+        <v>-0.3534</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4884</v>
+        <v>-0.1936</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0805</v>
+        <v>-0.1598</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6226</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.9931</v>
+        <v>6.3959</v>
       </c>
       <c r="E17" t="n">
-        <v>5.2551</v>
+        <v>5.1577</v>
       </c>
       <c r="F17" t="n">
-        <v>0.738</v>
+        <v>1.2382</v>
       </c>
       <c r="G17" t="n">
         <v>3.3066</v>
@@ -1780,13 +1780,13 @@
         <v>2.0757</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2945</v>
+        <v>0.1083</v>
       </c>
       <c r="T17" t="n">
-        <v>0.77</v>
+        <v>0.6726</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0646</v>
+        <v>-0.5643</v>
       </c>
       <c r="V17" t="n">
         <v>1.8488</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.7514</v>
+        <v>4.5625</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3659</v>
+        <v>3.0736</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3855</v>
+        <v>1.489</v>
       </c>
       <c r="G18" t="n">
         <v>3.6638</v>
@@ -1858,13 +1858,13 @@
         <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>0.465</v>
+        <v>0.2762</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7236</v>
+        <v>0.4313</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2586</v>
+        <v>-0.1551</v>
       </c>
       <c r="V18" t="n">
         <v>0.6226</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.8074</v>
+        <v>4.001</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6161</v>
+        <v>2.5186</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1913</v>
+        <v>1.4823</v>
       </c>
       <c r="G19" t="n">
         <v>3.3877</v>
@@ -1936,13 +1936,13 @@
         <v>2.2644</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9012</v>
+        <v>-0.7076</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2787</v>
+        <v>-0.3761</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.3315</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.9002</v>
+        <v>2.5073</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2804</v>
+        <v>0.1278</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6198</v>
+        <v>2.3796</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1185</v>
+        <v>0.2484</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7288</v>
+        <v>-1.0894</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3897</v>
+        <v>1.3377</v>
       </c>
       <c r="J20" t="n">
-        <v>2.3917</v>
+        <v>-0.0638</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2187</v>
+        <v>-1.3148</v>
       </c>
       <c r="L20" t="n">
-        <v>0.173</v>
+        <v>1.2509</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2732</v>
+        <v>0.3122</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4899</v>
+        <v>0.2254</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2167</v>
+        <v>0.0868</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7548</v>
+        <v>1.6983</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0757</v>
+        <v>1.6983</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1781</v>
+        <v>0.2399</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3608</v>
+        <v>0.1916</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1827</v>
+        <v>0.0483</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.3208</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.7567</v>
+        <v>1.0919</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.499</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4084</v>
+        <v>1.591</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2484</v>
+        <v>2.1185</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0894</v>
+        <v>1.7288</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3377</v>
+        <v>0.3897</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0638</v>
+        <v>2.3917</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3148</v>
+        <v>2.2187</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2509</v>
+        <v>0.173</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3122</v>
+        <v>-0.2732</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2254</v>
+        <v>-0.4899</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0868</v>
+        <v>0.2167</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6983</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6983</v>
+        <v>2.0757</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5108</v>
+        <v>0.3698</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5879</v>
+        <v>0.5813</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0771</v>
+        <v>-0.2116</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3208</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1957</v>
+        <v>0.2205</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6776</v>
+        <v>-0.2879</v>
       </c>
       <c r="F22" t="n">
-        <v>0.482</v>
+        <v>0.5084</v>
       </c>
       <c r="G22" t="n">
         <v>1.6735</v>
@@ -2170,13 +2170,13 @@
         <v>2.2644</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3033</v>
+        <v>-0.8871</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.4797</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4338</v>
+        <v>-0.4073</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8868</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>P. HURYNOWICZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.635</v>
+        <v>-0.5617</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8026</v>
+        <v>-1.3482</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1676</v>
+        <v>0.7865</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4344</v>
+        <v>-0.2161</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0925</v>
+        <v>0.1456</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6581</v>
+        <v>-0.3617</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0249</v>
+        <v>0.2296</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4601</v>
+        <v>0.8295</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.485</v>
+        <v>-0.5999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4593</v>
+        <v>-0.4457</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6324</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.173</v>
+        <v>0.2383</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1322</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6983</v>
+        <v>1.3209</v>
       </c>
       <c r="S23" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.2205</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1735</v>
+        <v>0.3092</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2552</v>
+        <v>-0.0887</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.019</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2262</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. HURYNOWICZ</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2859</v>
+        <v>-0.8467</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1277</v>
+        <v>-1.8026</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8417</v>
+        <v>0.956</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2161</v>
+        <v>0.4344</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1456</v>
+        <v>1.0925</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3617</v>
+        <v>-0.6581</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2296</v>
+        <v>-0.0249</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8295</v>
+        <v>0.4601</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5999</v>
+        <v>-0.485</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4457</v>
+        <v>0.4593</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.6324</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2383</v>
+        <v>-0.173</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.5661</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3209</v>
+        <v>1.6983</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5038</v>
+        <v>-0.1299</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4703</v>
+        <v>-0.1735</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0335</v>
+        <v>0.0436</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5035</v>
+        <v>-3.3712</v>
       </c>
       <c r="E25" t="n">
         <v>-5.3439</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8404</v>
+        <v>1.9727</v>
       </c>
       <c r="G25" t="n">
         <v>-5.6288</v>
@@ -2404,13 +2404,13 @@
         <v>2.4531</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6296</v>
+        <v>-0.4973</v>
       </c>
       <c r="T25" t="n">
         <v>-0.4551</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1745</v>
+        <v>-0.0423</v>
       </c>
       <c r="V25" t="n">
         <v>0.3018</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>20.059</v>
+        <v>20.7084</v>
       </c>
       <c r="E26" t="n">
-        <v>7.7111</v>
+        <v>7.711200000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>12.3479</v>
+        <v>12.9975</v>
       </c>
       <c r="G26" t="n">
         <v>16.4843</v>
@@ -2461,7 +2461,7 @@
         <v>13.4996</v>
       </c>
       <c r="L26" t="n">
-        <v>5.517300000000001</v>
+        <v>5.5173</v>
       </c>
       <c r="M26" t="n">
         <v>-2.5329</v>
@@ -2482,22 +2482,22 @@
         <v>19.8135</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.0104</v>
+        <v>-1.3606</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5077999999999998</v>
+        <v>0.508</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.518400000000001</v>
+        <v>-1.8687</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.0759999999999999</v>
+        <v>-0.07600000000000023</v>
       </c>
       <c r="W26" t="n">
         <v>2.3384</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.4144</v>
+        <v>-2.414400000000001</v>
       </c>
     </row>
   </sheetData>
